--- a/output/pdf_financials_xlsx/RDG.xlsx
+++ b/output/pdf_financials_xlsx/RDG.xlsx
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.274122</v>
+        <v>-1.274122</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.214302</v>
+        <v>-1.214302</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.9702499999999999</v>
+        <v>-0.9702499999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.903685</v>
+        <v>-0.903685</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.049876</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.274122</v>
+        <v>-1.274122</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.214302</v>
+        <v>-1.214302</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.9702499999999999</v>
+        <v>-0.9702499999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.903685</v>
+        <v>-0.903685</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-1.049876</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.274122</v>
+        <v>-1.274122</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.214302</v>
+        <v>-1.214302</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.9702499999999999</v>
+        <v>-0.9702499999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.903685</v>
+        <v>-0.903685</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-1.049876</v>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.274122</v>
+        <v>-1.274122</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.214302</v>
+        <v>-1.214302</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.9702499999999999</v>
+        <v>-0.9702499999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.903685</v>
+        <v>-0.903685</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.049876</v>
@@ -1184,16 +1184,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.292625</v>
+        <v>-1.255619</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.263351</v>
+        <v>-1.165253</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.049675</v>
+        <v>-0.890825</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.95989</v>
+        <v>-0.84748</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.968714</v>
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2769,7 +2769,7 @@
         <v>-1.076677</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.402219</v>
       </c>
     </row>
     <row r="92">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.663916</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.13413</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.265646</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.25623</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.584128</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -5028,7 +5028,11 @@
           <t>Revaluation reserves</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5074,7 +5078,11 @@
           <t>Foreign currency translation reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -5702,7 +5710,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.663916</v>
       </c>
@@ -6138,7 +6150,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -11238,19 +11254,19 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1.274122</v>
+        <v>-1.274122</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>1.214302</v>
+        <v>-1.214302</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.9702499999999999</v>
+        <v>-0.9702499999999999</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>0.903685</v>
+        <v>-0.903685</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>1.049876</v>
+        <v>-1.049876</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -11339,10 +11355,10 @@
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>0.58265</v>
+        <v>-0.58265</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>2.017793</v>
+        <v>-2.017793</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -12356,10 +12372,10 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>1.460467</v>
+        <v>-1.460467</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>0.58265</v>
+        <v>-0.58265</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -13113,10 +13129,10 @@
         </is>
       </c>
       <c r="F208" s="5" t="n">
-        <v>1.319236</v>
+        <v>-1.319236</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1.460467</v>
+        <v>-1.460467</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -13788,10 +13804,10 @@
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>1.118178</v>
+        <v>-1.118178</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>1.319236</v>
+        <v>-1.319236</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RDG.xlsx
+++ b/output/pdf_financials_xlsx/RDG.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010759</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00719</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022284</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039076</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014392</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.031273</v>
       </c>
     </row>
     <row r="13">
@@ -1134,22 +1134,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.274122</v>
+        <v>-1.263363</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.214302</v>
+        <v>-1.207112</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.9702499999999999</v>
+        <v>-0.947966</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.903685</v>
+        <v>-0.864609</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.049876</v>
+        <v>-1.064268</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.26118</v>
+        <v>0.229907</v>
       </c>
     </row>
     <row r="28">
@@ -1184,22 +1184,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.255619</v>
+        <v>-1.24486</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.165253</v>
+        <v>-1.158063</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.890825</v>
+        <v>-0.868541</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.84748</v>
+        <v>-0.808404</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.968714</v>
+        <v>-0.983106</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.348939</v>
+        <v>0.317666</v>
       </c>
     </row>
     <row r="30">
@@ -1315,22 +1315,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.758526</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.923225</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.186036</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.505053</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.602907</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.752219</v>
       </c>
     </row>
     <row r="35">
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.758526</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.923225</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.186036</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.505053</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.602907</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.752219</v>
       </c>
     </row>
     <row r="37">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.901884</v>
+        <v>0.143358</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.044028</v>
+        <v>0.120803</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.299424</v>
+        <v>0.113388</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.6662130000000001</v>
+        <v>0.16116</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.814483</v>
+        <v>0.211576</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.764004</v>
+        <v>2.011785</v>
       </c>
     </row>
     <row r="49">
@@ -3561,22 +3561,22 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016055</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027492</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017079</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025071</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019797</v>
       </c>
     </row>
     <row r="125">
@@ -3586,22 +3586,22 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016055</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027492</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017079</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025071</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019797</v>
       </c>
     </row>
     <row r="126">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -7364,7 +7364,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -8102,7 +8106,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8674,7 +8682,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>-0.016055</v>
       </c>
@@ -9024,7 +9036,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9890,7 +9906,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">

--- a/output/pdf_financials_xlsx/RDG.xlsx
+++ b/output/pdf_financials_xlsx/RDG.xlsx
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.274251</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.311683</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.253225</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.316128</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.261309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.343953</v>
       </c>
     </row>
     <row r="10">
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.344518</v>
+        <v>0.618769</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.376059</v>
+        <v>0.687742</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.315912</v>
+        <v>0.569137</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.320894</v>
+        <v>0.637022</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.296601</v>
+        <v>0.55791</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.976544</v>
+        <v>1.320497</v>
       </c>
     </row>
     <row r="11">
@@ -9520,7 +9520,11 @@
           <t>Personnel costs 15</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -9542,10 +9546,10 @@
         </is>
       </c>
       <c r="I127" s="5" t="n">
-        <v>-0.261309</v>
+        <v>0.261309</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>-0.343953</v>
+        <v>0.343953</v>
       </c>
     </row>
     <row r="128">
@@ -11036,7 +11040,11 @@
           <t>Personnel costs 14</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -12112,7 +12120,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -13048,7 +13060,11 @@
           <t>Personnel costs 11</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E206" s="5" t="n">
         <v>0.274251</v>
       </c>

--- a/output/pdf_financials_xlsx/RDG.xlsx
+++ b/output/pdf_financials_xlsx/RDG.xlsx
@@ -3248,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.058055</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01637</v>
       </c>
     </row>
     <row r="112">
@@ -3835,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.058055</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01637</v>
       </c>
     </row>
     <row r="135">
@@ -3860,10 +3860,10 @@
         <v>-0.8064210000000001</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.58677</v>
+        <v>-0.644825</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.707864</v>
+        <v>-0.724234</v>
       </c>
     </row>
   </sheetData>
@@ -6714,7 +6714,11 @@
           <t>Deferred tax expense 14</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -7186,7 +7190,11 @@
           <t>Purchase of equipment 6</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
